--- a/Results_experiment/exp_5/eval_cycle_XII.xlsx
+++ b/Results_experiment/exp_5/eval_cycle_XII.xlsx
@@ -447,13 +447,13 @@
         <v>530</v>
       </c>
       <c r="D2">
-        <v>-12.32046982292644</v>
+        <v>0.1491169287921958</v>
       </c>
       <c r="E2">
-        <v>29.60415629974246</v>
+        <v>7.482174946881082</v>
       </c>
       <c r="F2">
-        <v>21.84465674443065</v>
+        <v>5.569439024632832</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -467,13 +467,13 @@
         <v>509</v>
       </c>
       <c r="D3">
-        <v>-46.84880784949376</v>
+        <v>0.55549263560108</v>
       </c>
       <c r="E3">
-        <v>43.36198941858905</v>
+        <v>4.179392109882836</v>
       </c>
       <c r="F3">
-        <v>26.78821653009105</v>
+        <v>2.848428500292929</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -487,13 +487,13 @@
         <v>429</v>
       </c>
       <c r="D4">
-        <v>-71.97232521942246</v>
+        <v>0.2691881806908731</v>
       </c>
       <c r="E4">
-        <v>52.20774533811536</v>
+        <v>5.224667136633619</v>
       </c>
       <c r="F4">
-        <v>41.60360263970557</v>
+        <v>3.737369096900895</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -507,13 +507,13 @@
         <v>371</v>
       </c>
       <c r="D5">
-        <v>-30.73068643058156</v>
+        <v>0.3300485834101528</v>
       </c>
       <c r="E5">
-        <v>29.15928140046119</v>
+        <v>4.237002675865925</v>
       </c>
       <c r="F5">
-        <v>17.98261137168122</v>
+        <v>2.456073192272064</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -527,13 +527,13 @@
         <v>325</v>
       </c>
       <c r="D6">
-        <v>-17.37197641565126</v>
+        <v>-0.5651482678591715</v>
       </c>
       <c r="E6">
-        <v>22.48751017352636</v>
+        <v>6.563585934650328</v>
       </c>
       <c r="F6">
-        <v>15.97134017868684</v>
+        <v>4.80550475118252</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -547,13 +547,13 @@
         <v>235</v>
       </c>
       <c r="D7">
-        <v>-41.43626822980712</v>
+        <v>-2.686499986667927</v>
       </c>
       <c r="E7">
-        <v>27.92345855169958</v>
+        <v>8.230149679422519</v>
       </c>
       <c r="F7">
-        <v>17.68953705211269</v>
+        <v>6.7448967707601</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -567,13 +567,13 @@
         <v>223</v>
       </c>
       <c r="D8">
-        <v>-17.31079204862286</v>
+        <v>0.1389948463863144</v>
       </c>
       <c r="E8">
-        <v>20.36847519166462</v>
+        <v>4.416800961327869</v>
       </c>
       <c r="F8">
-        <v>12.3832876461771</v>
+        <v>3.361576681580779</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -587,13 +587,13 @@
         <v>84</v>
       </c>
       <c r="D9">
-        <v>-98.14165398333024</v>
+        <v>0.4701551930981873</v>
       </c>
       <c r="E9">
-        <v>85.832338988042</v>
+        <v>6.27476128862519</v>
       </c>
       <c r="F9">
-        <v>65.34881771675178</v>
+        <v>4.773821858423097</v>
       </c>
     </row>
   </sheetData>
